--- a/core/tests/testcases/basics/01_1nurse_1shift_1day.prettify.xlsx
+++ b/core/tests/testcases/basics/01_1nurse_1shift_1day.prettify.xlsx
@@ -34,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -55,27 +55,16 @@
         <color rgb="00374151"/>
       </bottom>
     </border>
-    <border>
-      <bottom style="medium">
-        <color rgb="00374151"/>
-      </bottom>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -443,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:B7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,69 +440,24 @@
       <c r="B1" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="inlineStr"/>
-      <c r="D1" s="1" t="inlineStr"/>
-      <c r="E1" s="2" t="inlineStr"/>
-      <c r="F1" s="1" t="inlineStr"/>
-      <c r="G1" s="1" t="inlineStr"/>
-      <c r="H1" s="2" t="inlineStr"/>
-      <c r="I1" s="2" t="inlineStr"/>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr"/>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr"/>
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Fri</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr"/>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>OFF (Total)</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>OFF (Weekday)</t>
-        </is>
-      </c>
-      <c r="F2" s="3" t="inlineStr">
-        <is>
-          <t>OFF (Weekend)</t>
-        </is>
-      </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>D Count</t>
-        </is>
-      </c>
-      <c r="H2" s="4" t="inlineStr"/>
-      <c r="I2" s="4" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr"/>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="G3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" s="4" t="inlineStr"/>
-      <c r="I3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -524,60 +468,32 @@
       <c r="B4" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="C4" s="2" t="inlineStr"/>
-      <c r="D4" s="1" t="inlineStr"/>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="1" t="inlineStr"/>
-      <c r="G4" s="1" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>OPTIMAL</t>
         </is>
       </c>
-      <c r="C5" s="4" t="inlineStr"/>
-      <c r="D5" s="3" t="inlineStr"/>
-      <c r="E5" s="4" t="inlineStr"/>
-      <c r="F5" s="3" t="inlineStr"/>
-      <c r="G5" s="3" t="inlineStr"/>
-      <c r="H5" s="4" t="inlineStr"/>
-      <c r="I5" s="4" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr"/>
       <c r="B6" s="1" t="inlineStr"/>
-      <c r="C6" s="2" t="inlineStr"/>
-      <c r="D6" s="1" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="1" t="inlineStr"/>
-      <c r="G6" s="1" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>D Count</t>
         </is>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="C7" s="4" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
-      <c r="E7" s="4" t="inlineStr"/>
-      <c r="F7" s="3" t="inlineStr"/>
-      <c r="G7" s="3" t="inlineStr"/>
-      <c r="H7" s="4" t="inlineStr"/>
-      <c r="I7" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/core/tests/testcases/basics/01_1nurse_1shift_1day.prettify.xlsx
+++ b/core/tests/testcases/basics/01_1nurse_1shift_1day.prettify.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,20 +481,6 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr"/>
-      <c r="B6" s="1" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>D Count</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
